--- a/days/tasks.xlsx
+++ b/days/tasks.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>апроб</t>
   </si>
@@ -43,6 +43,9 @@
   <si>
     <t>май</t>
   </si>
+  <si>
+    <t>Апробация</t>
+  </si>
 </sst>
 </file>
 
@@ -50,7 +53,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="167" formatCode="h:mm:ss;@"/>
+    <numFmt numFmtId="165" formatCode="h:mm:ss;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -301,13 +304,13 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -615,6 +618,9 @@
       <c r="G3" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="4" spans="2:9" s="18" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="C4" s="19">
@@ -631,6 +637,9 @@
       </c>
       <c r="G4" s="18" t="s">
         <v>5</v>
+      </c>
+      <c r="H4" s="20">
+        <v>46156</v>
       </c>
       <c r="I4" s="30"/>
     </row>

--- a/days/tasks.xlsx
+++ b/days/tasks.xlsx
@@ -55,7 +55,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="h:mm:ss;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,8 +78,14 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -128,8 +134,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor rgb="FFFBE5D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -217,11 +235,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -311,6 +366,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -574,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I31"/>
+  <dimension ref="B1:K31"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" style="1" customWidth="1"/>
@@ -584,7 +663,7 @@
     <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" s="26" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" s="26" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B1" s="21">
         <v>46088</v>
       </c>
@@ -597,12 +676,15 @@
       <c r="E1" s="24">
         <v>46123</v>
       </c>
-      <c r="F1" s="25">
+      <c r="G1" s="25">
         <v>46144</v>
       </c>
+      <c r="H1" s="31">
+        <v>46158</v>
+      </c>
       <c r="I1" s="28"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,7 +704,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:9" s="18" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" s="18" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="C4" s="19">
         <v>46085</v>
       </c>
@@ -643,7 +725,7 @@
       </c>
       <c r="I4" s="30"/>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -653,11 +735,15 @@
       <c r="D5" s="3"/>
       <c r="E5" s="4"/>
       <c r="G5" s="27"/>
-      <c r="I5" s="29">
+      <c r="H5" s="37"/>
+      <c r="J5" s="32">
         <v>1.0416666666666667E-3</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="K5" s="34">
+        <v>4.8611111111111112E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -667,11 +753,12 @@
       <c r="D6" s="3"/>
       <c r="E6" s="27"/>
       <c r="G6" s="27"/>
-      <c r="I6" s="29">
+      <c r="H6" s="33"/>
+      <c r="J6" s="32">
         <v>3.8194444444444443E-3</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -681,11 +768,12 @@
       <c r="D7" s="3"/>
       <c r="E7" s="27"/>
       <c r="G7" s="27"/>
-      <c r="I7" s="29">
+      <c r="H7" s="35"/>
+      <c r="J7" s="32">
         <v>3.8194444444444443E-3</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -694,8 +782,10 @@
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="27"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H8" s="33"/>
+      <c r="J8" s="29"/>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -704,8 +794,10 @@
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="27"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H9" s="33"/>
+      <c r="J9" s="29"/>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>6</v>
       </c>
@@ -715,11 +807,12 @@
       <c r="D10" s="3"/>
       <c r="E10" s="27"/>
       <c r="G10" s="27"/>
-      <c r="I10" s="29">
+      <c r="H10" s="33"/>
+      <c r="J10" s="32">
         <v>3.8194444444444443E-3</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>7</v>
       </c>
@@ -729,11 +822,12 @@
       <c r="D11" s="3"/>
       <c r="E11" s="4"/>
       <c r="G11" s="27"/>
-      <c r="I11" s="29">
+      <c r="H11" s="33"/>
+      <c r="J11" s="32">
         <v>3.1249999999999997E-3</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>8</v>
       </c>
@@ -743,11 +837,12 @@
       <c r="D12" s="3"/>
       <c r="E12" s="4"/>
       <c r="G12" s="27"/>
-      <c r="I12" s="29">
+      <c r="H12" s="33"/>
+      <c r="J12" s="32">
         <v>3.1249999999999997E-3</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>9</v>
       </c>
@@ -757,27 +852,32 @@
       <c r="D13" s="3"/>
       <c r="E13" s="4"/>
       <c r="G13" s="27"/>
-      <c r="I13" s="29">
+      <c r="H13" s="35"/>
+      <c r="J13" s="32">
         <v>3.1249999999999997E-3</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>10</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H14" s="33"/>
+      <c r="J14" s="29"/>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>11</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H15" s="33"/>
+      <c r="J15" s="29"/>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>12</v>
       </c>
@@ -785,11 +885,12 @@
       <c r="D16" s="3"/>
       <c r="E16" s="4"/>
       <c r="G16" s="27"/>
-      <c r="I16" s="29">
+      <c r="H16" s="33"/>
+      <c r="J16" s="32">
         <v>2.7777777777777779E-3</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>13</v>
       </c>
@@ -797,19 +898,22 @@
       <c r="D17" s="3"/>
       <c r="E17" s="4"/>
       <c r="G17" s="27"/>
-      <c r="I17" s="29">
+      <c r="H17" s="38"/>
+      <c r="J17" s="32">
         <v>5.5555555555555558E-3</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>14</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H18" s="33"/>
+      <c r="J18" s="29"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>15</v>
       </c>
@@ -817,35 +921,42 @@
       <c r="D19" s="6"/>
       <c r="E19" s="7"/>
       <c r="G19" s="27"/>
-      <c r="I19" s="29">
+      <c r="H19" s="33"/>
+      <c r="J19" s="32">
         <v>3.472222222222222E-3</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>16</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="9"/>
       <c r="E20" s="10"/>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H20" s="33"/>
+      <c r="J20" s="29"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>17</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="9"/>
       <c r="E21" s="10"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H21" s="33"/>
+      <c r="J21" s="29"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>18</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="12"/>
       <c r="E22" s="10"/>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H22" s="38"/>
+      <c r="J22" s="29"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="13">
         <v>19</v>
       </c>
@@ -853,11 +964,12 @@
       <c r="D23" s="9"/>
       <c r="E23" s="10"/>
       <c r="G23" s="27"/>
-      <c r="I23" s="29">
+      <c r="H23" s="33"/>
+      <c r="J23" s="32">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="13">
         <v>20</v>
       </c>
@@ -865,11 +977,12 @@
       <c r="D24" s="9"/>
       <c r="E24" s="10"/>
       <c r="G24" s="27"/>
-      <c r="I24" s="29">
+      <c r="H24" s="33"/>
+      <c r="J24" s="32">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="13">
         <v>21</v>
       </c>
@@ -877,11 +990,12 @@
       <c r="D25" s="15"/>
       <c r="E25" s="16"/>
       <c r="G25" s="27"/>
-      <c r="I25" s="29">
+      <c r="H25" s="33"/>
+      <c r="J25" s="32">
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>22</v>
       </c>
@@ -892,11 +1006,12 @@
         <v>1</v>
       </c>
       <c r="G26" s="27"/>
-      <c r="I26" s="29">
+      <c r="H26" s="35"/>
+      <c r="J26" s="32">
         <v>1.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>23</v>
       </c>
@@ -907,11 +1022,12 @@
         <v>1</v>
       </c>
       <c r="G27" s="27"/>
-      <c r="I27" s="29">
+      <c r="H27" s="33"/>
+      <c r="J27" s="32">
         <v>1.736111111111111E-3</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>24</v>
       </c>
@@ -922,11 +1038,12 @@
         <v>1</v>
       </c>
       <c r="G28" s="27"/>
-      <c r="I28" s="29">
+      <c r="H28" s="38"/>
+      <c r="J28" s="32">
         <v>5.5555555555555558E-3</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>25</v>
       </c>
@@ -937,11 +1054,15 @@
         <v>1</v>
       </c>
       <c r="G29" s="27"/>
-      <c r="I29" s="29">
+      <c r="H29" s="35"/>
+      <c r="J29" s="32">
         <v>1.3888888888888889E-3</v>
       </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="K29" s="34">
+        <v>9.7222222222222224E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>26</v>
       </c>
@@ -951,8 +1072,10 @@
       <c r="D30" s="17">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H30" s="38"/>
+      <c r="J30" s="29"/>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>27</v>
       </c>
@@ -963,8 +1086,12 @@
         <v>1</v>
       </c>
       <c r="G31" s="27"/>
-      <c r="I31" s="29">
+      <c r="H31" s="36"/>
+      <c r="J31" s="32">
         <v>4.2013888888888885E-2</v>
+      </c>
+      <c r="K31" s="34">
+        <v>3.2638888888888891E-2</v>
       </c>
     </row>
   </sheetData>

--- a/days/tasks.xlsx
+++ b/days/tasks.xlsx
@@ -52,7 +52,7 @@
     <numFmt numFmtId="165" formatCode="h:mm:ss;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,13 +88,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -273,159 +266,159 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -986,6 +979,7 @@
       <c r="D27" s="38" t="n">
         <v>1</v>
       </c>
+      <c r="F27" s="18"/>
       <c r="G27" s="19"/>
       <c r="H27" s="23"/>
       <c r="J27" s="21" t="n">
@@ -1018,6 +1012,7 @@
       <c r="D29" s="38" t="n">
         <v>1</v>
       </c>
+      <c r="F29" s="18"/>
       <c r="G29" s="19"/>
       <c r="H29" s="24"/>
       <c r="J29" s="21" t="n">

--- a/days/tasks.xlsx
+++ b/days/tasks.xlsx
@@ -94,7 +94,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -104,13 +104,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.7998"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFDEE7E5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.7998"/>
-        <bgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FFDEE7E5"/>
       </patternFill>
     </fill>
     <fill>
@@ -145,6 +145,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDEE7E5"/>
+        <bgColor rgb="FFDAE3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.05"/>
         <bgColor rgb="FFE2F0D9"/>
       </patternFill>
@@ -261,7 +267,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -366,6 +372,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -398,7 +408,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -452,7 +462,7 @@
       <rgbColor rgb="FF8FAADC"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFBE5D6"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFDEE7E5"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -615,7 +625,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="4" t="n">
         <v>46088</v>
       </c>
@@ -639,8 +649,7 @@
       </c>
       <c r="I1" s="11"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
@@ -660,7 +669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="13" t="n">
         <v>46085</v>
       </c>
@@ -681,7 +690,7 @@
       </c>
       <c r="I4" s="14"/>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
@@ -700,7 +709,7 @@
         <v>0.00486111111111111</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="n">
         <v>2</v>
       </c>
@@ -716,7 +725,7 @@
         <v>0.00381944444444444</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="n">
         <v>3</v>
       </c>
@@ -731,7 +740,7 @@
         <v>0.00381944444444444</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="n">
         <v>4</v>
       </c>
@@ -740,10 +749,11 @@
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="19"/>
+      <c r="F8" s="18"/>
       <c r="H8" s="23"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="n">
         <v>5</v>
       </c>
@@ -752,10 +762,11 @@
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="19"/>
+      <c r="F9" s="18"/>
       <c r="H9" s="23"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="n">
         <v>6</v>
       </c>
@@ -764,13 +775,14 @@
       </c>
       <c r="D10" s="16"/>
       <c r="E10" s="19"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="19"/>
       <c r="H10" s="23"/>
       <c r="J10" s="21" t="n">
         <v>0.00381944444444444</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="n">
         <v>7</v>
       </c>
@@ -779,13 +791,14 @@
       </c>
       <c r="D11" s="16"/>
       <c r="E11" s="17"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="19"/>
       <c r="H11" s="23"/>
       <c r="J11" s="21" t="n">
         <v>0.003125</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="n">
         <v>8</v>
       </c>
@@ -800,7 +813,7 @@
         <v>0.003125</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="n">
         <v>9</v>
       </c>
@@ -815,7 +828,7 @@
         <v>0.003125</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="n">
         <v>10</v>
       </c>
@@ -825,17 +838,18 @@
       <c r="H14" s="23"/>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
       <c r="E15" s="17"/>
+      <c r="F15" s="18"/>
       <c r="H15" s="23"/>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="n">
         <v>12</v>
       </c>
@@ -848,119 +862,121 @@
         <v>0.00277777777777778</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
       <c r="E17" s="17"/>
+      <c r="F17" s="18"/>
       <c r="G17" s="19"/>
       <c r="H17" s="25"/>
       <c r="J17" s="21" t="n">
         <v>0.00555555555555556</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="n">
         <v>14</v>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
+      <c r="F18" s="26"/>
       <c r="H18" s="23"/>
       <c r="J18" s="2"/>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="29"/>
       <c r="G19" s="19"/>
       <c r="H19" s="23"/>
       <c r="J19" s="21" t="n">
         <v>0.00347222222222222</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="31"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="32"/>
       <c r="H20" s="23"/>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="31"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="32"/>
       <c r="H21" s="23"/>
       <c r="J21" s="2"/>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C22" s="32"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="31"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="32"/>
       <c r="H22" s="25"/>
       <c r="J22" s="2"/>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="34" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="35" t="n">
         <v>19</v>
       </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="31"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="32"/>
       <c r="G23" s="19"/>
       <c r="H23" s="23"/>
       <c r="J23" s="21" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="34" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="31"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="32"/>
       <c r="G24" s="19"/>
       <c r="H24" s="23"/>
       <c r="J24" s="21" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="34" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="35" t="n">
         <v>21</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="37"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="38"/>
       <c r="G25" s="19"/>
       <c r="H25" s="23"/>
       <c r="J25" s="21" t="n">
         <v>0.0104166666666667</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="C26" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="38" t="n">
+      <c r="C26" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="39" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="19"/>
@@ -969,14 +985,14 @@
         <v>0.0166666666666667</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="C27" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="38" t="n">
+      <c r="C27" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="39" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="18"/>
@@ -986,14 +1002,14 @@
         <v>0.00173611111111111</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C28" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="38" t="n">
+      <c r="C28" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="39" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="19"/>
@@ -1002,14 +1018,14 @@
         <v>0.00555555555555556</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C29" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="38" t="n">
+      <c r="C29" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="39" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="18"/>
@@ -1022,32 +1038,33 @@
         <v>0.00972222222222222</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="C30" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="38" t="n">
-        <v>1</v>
-      </c>
+      <c r="C30" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="18"/>
       <c r="H30" s="25"/>
       <c r="J30" s="2"/>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C31" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="38" t="n">
+      <c r="D31" s="39" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="18"/>
       <c r="G31" s="19"/>
-      <c r="H31" s="39"/>
+      <c r="H31" s="40"/>
       <c r="J31" s="21" t="n">
         <v>0.0420138888888889</v>
       </c>

--- a/days/tasks.xlsx
+++ b/days/tasks.xlsx
@@ -94,7 +94,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -139,8 +139,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF729FCF"/>
+        <bgColor rgb="FF8FAADC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.3999"/>
-        <bgColor rgb="FF969696"/>
+        <bgColor rgb="FF729FCF"/>
       </patternFill>
     </fill>
     <fill>
@@ -348,7 +354,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -356,7 +362,55 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -364,54 +418,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -428,7 +434,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -490,7 +496,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF729FCF"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF00A933"/>
       <rgbColor rgb="FF003300"/>
@@ -871,7 +877,7 @@
       <c r="E17" s="17"/>
       <c r="F17" s="18"/>
       <c r="G17" s="19"/>
-      <c r="H17" s="25"/>
+      <c r="H17" s="23"/>
       <c r="J17" s="21" t="n">
         <v>0.00555555555555556</v>
       </c>
@@ -883,7 +889,7 @@
       <c r="C18" s="16"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
-      <c r="F18" s="26"/>
+      <c r="F18" s="25"/>
       <c r="H18" s="23"/>
       <c r="J18" s="2"/>
     </row>
@@ -891,9 +897,9 @@
       <c r="B19" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="29"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="28"/>
       <c r="G19" s="19"/>
       <c r="H19" s="23"/>
       <c r="J19" s="21" t="n">
@@ -904,9 +910,9 @@
       <c r="B20" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="32"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="31"/>
       <c r="H20" s="23"/>
       <c r="J20" s="2"/>
     </row>
@@ -914,9 +920,9 @@
       <c r="B21" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="32"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="31"/>
       <c r="H21" s="23"/>
       <c r="J21" s="2"/>
     </row>
@@ -924,47 +930,47 @@
       <c r="B22" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="32"/>
-      <c r="H22" s="25"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="31"/>
+      <c r="H22" s="23"/>
       <c r="J22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="35" t="n">
+      <c r="B23" s="34" t="n">
         <v>19</v>
       </c>
-      <c r="C23" s="30"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="32"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="31"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="23"/>
+      <c r="H23" s="35"/>
       <c r="J23" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="35" t="n">
+      <c r="B24" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="C24" s="30"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="32"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="31"/>
       <c r="G24" s="19"/>
-      <c r="H24" s="23"/>
+      <c r="H24" s="35"/>
       <c r="J24" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="35" t="n">
+      <c r="B25" s="34" t="n">
         <v>21</v>
       </c>
       <c r="C25" s="36"/>
       <c r="D25" s="37"/>
       <c r="E25" s="38"/>
       <c r="G25" s="19"/>
-      <c r="H25" s="23"/>
+      <c r="H25" s="35"/>
       <c r="J25" s="21" t="n">
         <v>0.0104166666666667</v>
       </c>
@@ -997,7 +1003,7 @@
       </c>
       <c r="F27" s="18"/>
       <c r="G27" s="19"/>
-      <c r="H27" s="23"/>
+      <c r="H27" s="35"/>
       <c r="J27" s="21" t="n">
         <v>0.00173611111111111</v>
       </c>
@@ -1013,7 +1019,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="19"/>
-      <c r="H28" s="25"/>
+      <c r="H28" s="23"/>
       <c r="J28" s="21" t="n">
         <v>0.00555555555555556</v>
       </c>
@@ -1049,7 +1055,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="18"/>
-      <c r="H30" s="25"/>
+      <c r="H30" s="23"/>
       <c r="J30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/days/tasks.xlsx
+++ b/days/tasks.xlsx
@@ -94,7 +94,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -134,13 +134,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.3999"/>
-        <bgColor rgb="FFFF99CC"/>
+        <bgColor rgb="FFC0C0C0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF729FCF"/>
         <bgColor rgb="FF8FAADC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE78BE2"/>
+        <bgColor rgb="FFCC99FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -273,7 +279,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -318,7 +324,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -362,7 +368,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -370,11 +376,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -410,7 +420,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -486,7 +496,7 @@
       <rgbColor rgb="FFE2F0D9"/>
       <rgbColor rgb="FFFFFFA6"/>
       <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFE78BE2"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFF4B183"/>
       <rgbColor rgb="FF3366FF"/>
@@ -653,7 +663,9 @@
       <c r="H1" s="10" t="n">
         <v>46158</v>
       </c>
-      <c r="I1" s="11"/>
+      <c r="I1" s="11" t="n">
+        <v>46172</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="1" t="s">
@@ -740,8 +752,9 @@
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="19"/>
+      <c r="F7" s="24"/>
       <c r="G7" s="19"/>
-      <c r="H7" s="24"/>
+      <c r="H7" s="25"/>
       <c r="J7" s="21" t="n">
         <v>0.00381944444444444</v>
       </c>
@@ -756,6 +769,7 @@
       <c r="D8" s="16"/>
       <c r="E8" s="19"/>
       <c r="F8" s="18"/>
+      <c r="G8" s="24"/>
       <c r="H8" s="23"/>
       <c r="J8" s="2"/>
     </row>
@@ -769,6 +783,7 @@
       <c r="D9" s="16"/>
       <c r="E9" s="19"/>
       <c r="F9" s="18"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="23"/>
       <c r="J9" s="2"/>
     </row>
@@ -813,6 +828,7 @@
       </c>
       <c r="D12" s="16"/>
       <c r="E12" s="17"/>
+      <c r="F12" s="24"/>
       <c r="G12" s="19"/>
       <c r="H12" s="23"/>
       <c r="J12" s="21" t="n">
@@ -828,8 +844,9 @@
       </c>
       <c r="D13" s="16"/>
       <c r="E13" s="17"/>
+      <c r="F13" s="24"/>
       <c r="G13" s="19"/>
-      <c r="H13" s="24"/>
+      <c r="H13" s="25"/>
       <c r="J13" s="21" t="n">
         <v>0.003125</v>
       </c>
@@ -889,7 +906,8 @@
       <c r="C18" s="16"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
-      <c r="F18" s="25"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="24"/>
       <c r="H18" s="23"/>
       <c r="J18" s="2"/>
     </row>
@@ -897,9 +915,9 @@
       <c r="B19" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="29"/>
       <c r="G19" s="19"/>
       <c r="H19" s="23"/>
       <c r="J19" s="21" t="n">
@@ -910,9 +928,9 @@
       <c r="B20" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="31"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="32"/>
       <c r="H20" s="23"/>
       <c r="J20" s="2"/>
     </row>
@@ -920,9 +938,9 @@
       <c r="B21" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="31"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="32"/>
       <c r="H21" s="23"/>
       <c r="J21" s="2"/>
     </row>
@@ -930,47 +948,47 @@
       <c r="B22" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C22" s="32"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="31"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="32"/>
       <c r="H22" s="23"/>
       <c r="J22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="34" t="n">
+      <c r="B23" s="35" t="n">
         <v>19</v>
       </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="31"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="32"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="35"/>
+      <c r="H23" s="36"/>
       <c r="J23" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="34" t="n">
+      <c r="B24" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="31"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="32"/>
       <c r="G24" s="19"/>
-      <c r="H24" s="35"/>
+      <c r="H24" s="36"/>
       <c r="J24" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="34" t="n">
+      <c r="B25" s="35" t="n">
         <v>21</v>
       </c>
-      <c r="C25" s="36"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="38"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="39"/>
       <c r="G25" s="19"/>
-      <c r="H25" s="35"/>
+      <c r="H25" s="36"/>
       <c r="J25" s="21" t="n">
         <v>0.0104166666666667</v>
       </c>
@@ -979,14 +997,14 @@
       <c r="B26" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="C26" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="39" t="n">
+      <c r="C26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="40" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="19"/>
-      <c r="H26" s="24"/>
+      <c r="H26" s="25"/>
       <c r="J26" s="21" t="n">
         <v>0.0166666666666667</v>
       </c>
@@ -995,15 +1013,16 @@
       <c r="B27" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="C27" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="39" t="n">
-        <v>1</v>
-      </c>
+      <c r="C27" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="24"/>
       <c r="F27" s="18"/>
       <c r="G27" s="19"/>
-      <c r="H27" s="35"/>
+      <c r="H27" s="36"/>
       <c r="J27" s="21" t="n">
         <v>0.00173611111111111</v>
       </c>
@@ -1012,10 +1031,10 @@
       <c r="B28" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C28" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="39" t="n">
+      <c r="C28" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="40" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="19"/>
@@ -1028,15 +1047,16 @@
       <c r="B29" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C29" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="39" t="n">
-        <v>1</v>
-      </c>
+      <c r="C29" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="24"/>
       <c r="F29" s="18"/>
       <c r="G29" s="19"/>
-      <c r="H29" s="24"/>
+      <c r="H29" s="25"/>
       <c r="J29" s="21" t="n">
         <v>0.00138888888888889</v>
       </c>
@@ -1048,10 +1068,10 @@
       <c r="B30" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="C30" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="39" t="n">
+      <c r="C30" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="40" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="18"/>
@@ -1065,12 +1085,12 @@
       <c r="C31" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="39" t="n">
+      <c r="D31" s="40" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="18"/>
       <c r="G31" s="19"/>
-      <c r="H31" s="40"/>
+      <c r="H31" s="41"/>
       <c r="J31" s="21" t="n">
         <v>0.0420138888888889</v>
       </c>

--- a/days/tasks.xlsx
+++ b/days/tasks.xlsx
@@ -1003,6 +1003,7 @@
       <c r="D26" s="40" t="n">
         <v>1</v>
       </c>
+      <c r="E26" s="24"/>
       <c r="G26" s="19"/>
       <c r="H26" s="25"/>
       <c r="J26" s="21" t="n">
@@ -1037,6 +1038,7 @@
       <c r="D28" s="40" t="n">
         <v>1</v>
       </c>
+      <c r="E28" s="24"/>
       <c r="G28" s="19"/>
       <c r="H28" s="23"/>
       <c r="J28" s="21" t="n">
@@ -1074,6 +1076,7 @@
       <c r="D30" s="40" t="n">
         <v>1</v>
       </c>
+      <c r="E30" s="24"/>
       <c r="F30" s="18"/>
       <c r="H30" s="23"/>
       <c r="J30" s="2"/>
